--- a/order_forms/018_wedding_cake_order_form--order_forms.xlsx
+++ b/order_forms/018_wedding_cake_order_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -849,8 +849,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'round',_'value':_'round'}</t>
+          <t>round</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'round', 'value': 'Round'}</t>
+          <t>Round</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'heart',_'value':_'heart'}</t>
+          <t>heart</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'heart', 'value': 'Heart'}</t>
+          <t>Heart</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'square',_'value':_'square'}</t>
+          <t>square</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'square', 'value': 'Square'}</t>
+          <t>Square</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'small',_'value':_'small'}</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'small', 'value': 'Small'}</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium',_'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'medium', 'value': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'large',_'value':_'large'}</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'large', 'value': 'Large'}</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'extra_large',_'value':_'extra_large'}</t>
+          <t>extra_large</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'extra_large', 'value': 'Extra Large'}</t>
+          <t>Extra Large</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'extra_extra_large',_'value':_'extra_extra_large'}</t>
+          <t>extra_extra_large</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'extra_extra_large', 'value': 'Extra Extra Large'}</t>
+          <t>Extra Extra Large</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'strawberry',_'value':_'strawberry'}</t>
+          <t>strawberry</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'strawberry', 'value': 'Strawberry'}</t>
+          <t>Strawberry</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'chocolate',_'value':_'chocolate'}</t>
+          <t>chocolate</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'chocolate', 'value': 'Chocolate'}</t>
+          <t>Chocolate</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'jimmy',_'value':_'jimmy'}</t>
+          <t>jimmy</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'jimmy', 'value': 'Jimmy'}</t>
+          <t>Jimmy</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'tom',_'value':_'tom'}</t>
+          <t>tom</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'tom', 'value': 'Tom'}</t>
+          <t>Tom</t>
         </is>
       </c>
     </row>
